--- a/data/trans_dic/P34B03_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,2; 23,15</t>
+          <t>15,23; 22,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 25,66</t>
+          <t>17,46; 26,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 26,28</t>
+          <t>18,38; 26,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,46</t>
+          <t>11,19; 19,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 20,36</t>
+          <t>12,22; 20,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,93</t>
+          <t>13,52; 20,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,52</t>
+          <t>14,45; 20,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 21,82</t>
+          <t>15,91; 21,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,6</t>
+          <t>17,05; 22,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 26,81</t>
+          <t>18,22; 27,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 25,92</t>
+          <t>17,37; 25,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 25,54</t>
+          <t>16,92; 25,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,62</t>
+          <t>7,32; 14,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 19,01</t>
+          <t>10,97; 18,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,15</t>
+          <t>9,64; 15,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,26; 20,23</t>
+          <t>14,36; 20,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 20,82</t>
+          <t>15,33; 21,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,01</t>
+          <t>14,34; 20,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,88</t>
+          <t>10,73; 16,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,85</t>
+          <t>10,83; 16,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 17,38</t>
+          <t>4,18; 17,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,49</t>
+          <t>4,23; 10,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,88</t>
+          <t>4,65; 13,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,19</t>
+          <t>4,16; 12,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 14,15</t>
+          <t>9,72; 14,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 14,95</t>
+          <t>9,83; 14,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,85</t>
+          <t>4,53; 14,67</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 14,84</t>
+          <t>10,61; 14,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,62</t>
+          <t>10,64; 14,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,08</t>
+          <t>10,3; 15,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,3</t>
+          <t>4,62; 8,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,62</t>
+          <t>8,09; 12,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,47</t>
+          <t>3,94; 10,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,46</t>
+          <t>8,68; 11,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 13,2</t>
+          <t>10,25; 13,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,68</t>
+          <t>7,52; 12,5</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,37</t>
+          <t>7,39; 12,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,21</t>
+          <t>8,96; 14,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 21,9</t>
+          <t>12,24; 21,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,01</t>
+          <t>2,94; 6,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,31</t>
+          <t>4,66; 8,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,22</t>
+          <t>1,97; 4,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,8</t>
+          <t>5,16; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,22</t>
+          <t>7,15; 10,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,96</t>
+          <t>5,81; 9,92</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 33,82</t>
+          <t>22,67; 33,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,19; 44,69</t>
+          <t>33,68; 45,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,6; 40,31</t>
+          <t>21,93; 41,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,34</t>
+          <t>3,65; 6,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,46</t>
+          <t>6,22; 9,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,05</t>
+          <t>4,81; 9,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,83; 10,92</t>
+          <t>7,81; 10,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,37</t>
+          <t>12,63; 16,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,14</t>
+          <t>9,81; 15,54</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,33; 16,81</t>
+          <t>14,42; 16,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,55; 18,12</t>
+          <t>15,6; 18,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,23; 18,67</t>
+          <t>13,12; 18,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,43</t>
+          <t>5,82; 7,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 10,6</t>
+          <t>8,54; 10,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,0</t>
+          <t>6,48; 9,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,27; 11,79</t>
+          <t>10,25; 11,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 13,93</t>
+          <t>12,29; 13,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 13,43</t>
+          <t>10,34; 13,37</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66473; 101195</t>
+          <t>66594; 100457</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75294; 110092</t>
+          <t>74906; 111553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92042; 132770</t>
+          <t>92868; 135465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34102; 61201</t>
+          <t>35185; 60301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42623; 70663</t>
+          <t>42423; 70230</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58548; 89168</t>
+          <t>60503; 91104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110403; 154262</t>
+          <t>108612; 153521</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125646; 169347</t>
+          <t>123517; 168853</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>163454; 215345</t>
+          <t>162445; 213776</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75967; 112297</t>
+          <t>76286; 114044</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62609; 97778</t>
+          <t>65518; 97223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76639; 115485</t>
+          <t>76533; 115373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24797; 49418</t>
+          <t>24745; 48531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42413; 70781</t>
+          <t>40833; 70384</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36585; 57870</t>
+          <t>36831; 58709</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>107923; 153129</t>
+          <t>108643; 154357</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111669; 156012</t>
+          <t>114876; 158378</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121402; 166865</t>
+          <t>119651; 166926</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68204; 106125</t>
+          <t>67430; 106010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58236; 87949</t>
+          <t>56535; 87435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21249; 116143</t>
+          <t>27914; 117445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10527; 27290</t>
+          <t>11004; 26953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7324; 21395</t>
+          <t>7723; 22560</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7114; 20353</t>
+          <t>6937; 20101</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85639; 125719</t>
+          <t>86340; 127671</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68150; 102840</t>
+          <t>67622; 102540</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31080; 124019</t>
+          <t>37795; 122533</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123218; 172001</t>
+          <t>123012; 168356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122486; 168092</t>
+          <t>122348; 169881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>108441; 166203</t>
+          <t>106439; 164012</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35383; 63491</t>
+          <t>35299; 62683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69521; 104209</t>
+          <t>66839; 103200</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37158; 102328</t>
+          <t>38499; 100725</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>168743; 220455</t>
+          <t>166939; 222131</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>201823; 260692</t>
+          <t>202508; 258096</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>147928; 254953</t>
+          <t>151244; 251443</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37700; 63158</t>
+          <t>37716; 63875</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55906; 88178</t>
+          <t>55591; 87798</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59158; 103806</t>
+          <t>58012; 102170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22316; 45753</t>
+          <t>22394; 45777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32785; 61335</t>
+          <t>34438; 60844</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17154; 35430</t>
+          <t>16524; 33725</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64472; 99258</t>
+          <t>65664; 100129</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95278; 138832</t>
+          <t>97228; 139503</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77786; 130784</t>
+          <t>76267; 130293</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61091; 89875</t>
+          <t>60232; 89289</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>95299; 128318</t>
+          <t>96706; 130540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51950; 96937</t>
+          <t>52740; 98819</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40275; 70348</t>
+          <t>40458; 69870</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67645; 102395</t>
+          <t>67295; 103267</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36823; 68771</t>
+          <t>36540; 69864</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>107614; 150108</t>
+          <t>107443; 151145</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>170906; 224094</t>
+          <t>172882; 222937</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93972; 151465</t>
+          <t>98103; 155441</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>490058; 574798</t>
+          <t>493055; 580197</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>526395; 613530</t>
+          <t>528156; 614251</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>446297; 630017</t>
+          <t>442583; 629564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204159; 263567</t>
+          <t>206380; 267248</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>304465; 374524</t>
+          <t>301609; 375558</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>228787; 321704</t>
+          <t>231665; 323549</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>715630; 821517</t>
+          <t>714087; 818468</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>849926; 963354</t>
+          <t>849850; 964399</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>737411; 933076</t>
+          <t>718238; 929045</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B03_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,23; 22,98</t>
+          <t>15,51; 23,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 26,0</t>
+          <t>17,44; 25,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,38; 26,81</t>
+          <t>17,98; 25,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 19,18</t>
+          <t>11,11; 19,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,22; 20,24</t>
+          <t>12,2; 20,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 20,36</t>
+          <t>13,29; 19,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 20,42</t>
+          <t>14,36; 20,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,91; 21,76</t>
+          <t>15,89; 21,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,44</t>
+          <t>16,77; 21,57</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 27,23</t>
+          <t>18,06; 27,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,37; 25,77</t>
+          <t>17,19; 25,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 25,51</t>
+          <t>16,43; 24,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,36</t>
+          <t>7,1; 14,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 18,91</t>
+          <t>11,08; 18,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,37</t>
+          <t>9,74; 15,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 20,4</t>
+          <t>14,03; 19,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 21,13</t>
+          <t>15,32; 21,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,01</t>
+          <t>13,87; 19,18</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,87</t>
+          <t>11,16; 16,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 16,75</t>
+          <t>11,01; 17,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 17,57</t>
+          <t>12,93; 20,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,36</t>
+          <t>3,96; 10,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 13,58</t>
+          <t>4,48; 12,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,04</t>
+          <t>4,71; 12,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,37</t>
+          <t>9,53; 14,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,9</t>
+          <t>10,08; 15,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,67</t>
+          <t>11,3; 16,72</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,53</t>
+          <t>10,53; 14,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,78</t>
+          <t>10,68; 14,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 15,86</t>
+          <t>10,79; 15,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,2</t>
+          <t>4,65; 8,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,5</t>
+          <t>8,45; 12,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,3</t>
+          <t>7,71; 11,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,55</t>
+          <t>8,65; 11,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 13,06</t>
+          <t>10,13; 13,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,5</t>
+          <t>9,98; 13,1</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,51</t>
+          <t>7,33; 12,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,14</t>
+          <t>8,98; 14,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 21,55</t>
+          <t>12,33; 19,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,01</t>
+          <t>3,0; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,24</t>
+          <t>4,62; 8,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,02</t>
+          <t>2,69; 4,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,87</t>
+          <t>5,1; 7,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,27</t>
+          <t>7,04; 10,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,92</t>
+          <t>6,99; 10,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,67; 33,6</t>
+          <t>23,24; 34,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,68; 45,46</t>
+          <t>33,66; 44,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,93; 41,09</t>
+          <t>22,8; 40,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,3</t>
+          <t>3,64; 6,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,54</t>
+          <t>6,16; 9,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,2</t>
+          <t>5,24; 9,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,99</t>
+          <t>7,96; 10,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,63; 16,28</t>
+          <t>12,34; 16,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,54</t>
+          <t>9,97; 15,3</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 16,97</t>
+          <t>14,34; 16,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 18,14</t>
+          <t>15,58; 18,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,12; 18,66</t>
+          <t>16,16; 19,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,53</t>
+          <t>5,79; 7,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,63</t>
+          <t>8,64; 10,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,06</t>
+          <t>7,76; 9,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 11,75</t>
+          <t>10,24; 11,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 13,94</t>
+          <t>12,21; 13,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 13,37</t>
+          <t>12,19; 13,87</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112915</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>186910</t>
+          <t>198296</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66594; 100457</t>
+          <t>67810; 101687</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74906; 111553</t>
+          <t>74850; 108149</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92868; 135465</t>
+          <t>99017; 142022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35185; 60301</t>
+          <t>34927; 61057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42423; 70230</t>
+          <t>42330; 69862</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60503; 91104</t>
+          <t>64931; 96132</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>108612; 153521</t>
+          <t>107950; 150561</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>123517; 168853</t>
+          <t>123342; 167845</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>162445; 213776</t>
+          <t>174253; 224098</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94784</t>
+          <t>96754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>141899</t>
+          <t>148620</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76286; 114044</t>
+          <t>75634; 113503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65518; 97223</t>
+          <t>64859; 96997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76533; 115373</t>
+          <t>79402; 119697</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24745; 48531</t>
+          <t>24002; 49367</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40833; 70384</t>
+          <t>41230; 67622</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36831; 58709</t>
+          <t>41162; 65022</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>108643; 154357</t>
+          <t>106183; 149303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>114876; 158378</t>
+          <t>114787; 158489</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119651; 166926</t>
+          <t>125654; 173714</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69157</t>
+          <t>76602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>90740</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67430; 106010</t>
+          <t>70114; 105155</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56535; 87435</t>
+          <t>57475; 90157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27914; 117445</t>
+          <t>60993; 96525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11004; 26953</t>
+          <t>10293; 26419</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7723; 22560</t>
+          <t>7444; 21534</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6937; 20101</t>
+          <t>8836; 22872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86340; 127671</t>
+          <t>84728; 125838</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67622; 102540</t>
+          <t>69378; 103534</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37795; 122533</t>
+          <t>74493; 110223</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133668</t>
+          <t>146139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75060</t>
+          <t>81223</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>208728</t>
+          <t>227363</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123012; 168356</t>
+          <t>122018; 169644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122348; 169881</t>
+          <t>122813; 167193</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106439; 164012</t>
+          <t>121932; 177322</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35299; 62683</t>
+          <t>35596; 62661</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66839; 103200</t>
+          <t>69749; 103141</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38499; 100725</t>
+          <t>66380; 98886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>166939; 222131</t>
+          <t>166401; 220537</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>202508; 258096</t>
+          <t>200023; 257785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>151244; 251443</t>
+          <t>198603; 260783</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77763</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102605</t>
+          <t>120165</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37716; 63875</t>
+          <t>37411; 63400</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55591; 87798</t>
+          <t>55757; 88518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58012; 102170</t>
+          <t>69877; 113252</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22394; 45777</t>
+          <t>22823; 44305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34438; 60844</t>
+          <t>34092; 59767</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16524; 33725</t>
+          <t>22357; 40169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65664; 100129</t>
+          <t>64918; 100433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97228; 139503</t>
+          <t>95661; 138382</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76267; 130293</t>
+          <t>97675; 147708</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72219</t>
+          <t>74121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>59436</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>122797</t>
+          <t>133557</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>60232; 89289</t>
+          <t>61747; 91199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>96706; 130540</t>
+          <t>96651; 129037</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52740; 98819</t>
+          <t>54095; 96241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40458; 69870</t>
+          <t>40364; 69920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67295; 103267</t>
+          <t>66658; 103885</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36540; 69864</t>
+          <t>44160; 78210</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>107443; 151145</t>
+          <t>109461; 150538</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>172882; 222937</t>
+          <t>168993; 225666</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98103; 155441</t>
+          <t>107603; 165191</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560506</t>
+          <t>604320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>283849</t>
+          <t>314421</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>844355</t>
+          <t>918741</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>493055; 580197</t>
+          <t>490320; 580259</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>528156; 614251</t>
+          <t>527429; 614157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>442583; 629564</t>
+          <t>555797; 662244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206380; 267248</t>
+          <t>205444; 262318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>301609; 375558</t>
+          <t>305295; 375441</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>231665; 323549</t>
+          <t>281817; 345859</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>714087; 818468</t>
+          <t>713278; 820536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>849850; 964399</t>
+          <t>844919; 960884</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>718238; 929045</t>
+          <t>862055; 980554</t>
         </is>
       </c>
     </row>
